--- a/New_Outputs/Table2_Regression_NRS_HT4_HT6.xlsx
+++ b/New_Outputs/Table2_Regression_NRS_HT4_HT6.xlsx
@@ -12,27 +12,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t xml:space="preserve">Predictor</t>
   </si>
   <si>
-    <t xml:space="preserve">Hydrocodone group: ROE + 5-HT4 + 5-HT6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydrocodone group: + 5-HT4 x 5-HT6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydrocodone group: + Sex, MQS, SOWS, DOU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tramadol group: ROE + 5-HT4 + 5-HT6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tramadol group: + 5-HT4 x 5-HT6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tramadol group: + Sex, MQS, SOWS, DOU</t>
+    <t xml:space="preserve">Hydrocodone group: M3 ROE + 5-HT4 + 5-HT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrocodone group: M4 + ROE x 5-HT4 + ROE x 5-HT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrocodone group: M5 + Sex, log MME, MQS non-opioid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tramadol group: M3 ROE + 5-HT4 + 5-HT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tramadol group: M4 + ROE x 5-HT4 + ROE x 5-HT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tramadol group: M5 + Sex, log MME, MQS non-opioid</t>
   </si>
   <si>
     <t xml:space="preserve">Intercept</t>
@@ -41,19 +41,19 @@
     <t xml:space="preserve">10.238***</t>
   </si>
   <si>
-    <t xml:space="preserve">10.368***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.935**</t>
+    <t xml:space="preserve">9.902***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.828</t>
   </si>
   <si>
     <t xml:space="preserve">-10.191</t>
   </si>
   <si>
-    <t xml:space="preserve">-10.962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.315</t>
+    <t xml:space="preserve">-7.026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.565</t>
   </si>
   <si>
     <t xml:space="preserve">log10 ROE</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">1.412*</t>
   </si>
   <si>
-    <t xml:space="preserve">1.487*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784</t>
+    <t xml:space="preserve">1.278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.052</t>
   </si>
   <si>
     <t xml:space="preserve">-4.367**</t>
   </si>
   <si>
-    <t xml:space="preserve">-4.495**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.432*</t>
+    <t xml:space="preserve">-3.533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.286</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT4 activity</t>
@@ -83,19 +83,19 @@
     <t xml:space="preserve">2.463**</t>
   </si>
   <si>
-    <t xml:space="preserve">2.752*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.521*</t>
+    <t xml:space="preserve">0.587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.792</t>
   </si>
   <si>
     <t xml:space="preserve">-0.961</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835</t>
+    <t xml:space="preserve">5.833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.886</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT6 activity</t>
@@ -104,67 +104,79 @@
     <t xml:space="preserve">0.602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.932</t>
+    <t xml:space="preserve">-1.238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.496</t>
   </si>
   <si>
     <t xml:space="preserve">6.104**</t>
   </si>
   <si>
-    <t xml:space="preserve">5.615*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-HT4 x 5-HT6</t>
+    <t xml:space="preserve">35.699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-HT4 x log10 ROE</t>
   </si>
   <si>
     <t xml:space="preserve">--</t>
   </si>
   <si>
-    <t xml:space="preserve">2.457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.392</t>
+    <t xml:space="preserve">-0.835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-HT6 x log10 ROE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.195</t>
   </si>
   <si>
     <t xml:space="preserve">Sex (female = 1)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.873</t>
+    <t xml:space="preserve">1.242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log10 MME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626</t>
   </si>
   <si>
     <t xml:space="preserve">MQS non-opioid</t>
   </si>
   <si>
-    <t xml:space="preserve">0.049**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOWS withdrawal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.220*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duration of opioid use (yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.096*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.007</t>
+    <t xml:space="preserve">0.096**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.042</t>
   </si>
   <si>
     <t xml:space="preserve">n</t>
@@ -173,28 +185,34 @@
     <t xml:space="preserve">19</t>
   </si>
   <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
     <t xml:space="preserve">adj. R2</t>
   </si>
   <si>
     <t xml:space="preserve">0.459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839</t>
+    <t xml:space="preserve">0.402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771</t>
   </si>
   <si>
     <t xml:space="preserve">0.514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620</t>
+    <t xml:space="preserve">0.559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461</t>
   </si>
   <si>
     <t xml:space="preserve">model p</t>
@@ -203,16 +221,16 @@
     <t xml:space="preserve">0.006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7e-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.017</t>
+    <t xml:space="preserve">0.034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.222</t>
   </si>
 </sst>
 </file>
@@ -677,45 +695,45 @@
       <c r="C6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>36</v>
+      <c r="D6" t="s">
+        <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>36</v>
+      <c r="C7" t="s">
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>36</v>
+      <c r="F7" t="s">
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>36</v>
@@ -724,7 +742,7 @@
         <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>36</v>
@@ -733,12 +751,12 @@
         <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>36</v>
@@ -747,7 +765,7 @@
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>36</v>
@@ -756,12 +774,12 @@
         <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>36</v>
@@ -770,7 +788,7 @@
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>36</v>
@@ -779,76 +797,76 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/New_Outputs/Table2_Regression_NRS_HT4_HT6.xlsx
+++ b/New_Outputs/Table2_Regression_NRS_HT4_HT6.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t xml:space="preserve">Predictor</t>
   </si>
@@ -38,85 +38,85 @@
     <t xml:space="preserve">Intercept</t>
   </si>
   <si>
-    <t xml:space="preserve">10.238***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.902***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.565</t>
+    <t xml:space="preserve">6.713***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.060***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.573**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.379*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.066</t>
   </si>
   <si>
     <t xml:space="preserve">log10 ROE</t>
   </si>
   <si>
-    <t xml:space="preserve">1.412*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.367**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.286</t>
+    <t xml:space="preserve">0.126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.180</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT4 activity</t>
   </si>
   <si>
-    <t xml:space="preserve">2.463**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.886</t>
+    <t xml:space="preserve">2.617*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-12.253</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT6 activity</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.104**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.748</t>
+    <t xml:space="preserve">-0.866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.165*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.948</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT4 x log10 ROE</t>
@@ -125,112 +125,115 @@
     <t xml:space="preserve">--</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.266</t>
+    <t xml:space="preserve">-0.389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.910</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT6 x log10 ROE</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.195</t>
+    <t xml:space="preserve">1.777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.900</t>
   </si>
   <si>
     <t xml:space="preserve">Sex (female = 1)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.498</t>
+    <t xml:space="preserve">0.709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294</t>
   </si>
   <si>
     <t xml:space="preserve">log10 MME</t>
   </si>
   <si>
-    <t xml:space="preserve">1.484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.626</t>
+    <t xml:space="preserve">2.941**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.571</t>
   </si>
   <si>
     <t xml:space="preserve">MQS non-opioid</t>
   </si>
   <si>
-    <t xml:space="preserve">0.096**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.042</t>
+    <t xml:space="preserve">0.071*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102</t>
   </si>
   <si>
     <t xml:space="preserve">n</t>
   </si>
   <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
   </si>
   <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
     <t xml:space="preserve">adj. R2</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461</t>
+    <t xml:space="preserve">0.188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.041</t>
   </si>
   <si>
     <t xml:space="preserve">model p</t>
   </si>
   <si>
-    <t xml:space="preserve">0.006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.222</t>
+    <t xml:space="preserve">0.074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8e-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455</t>
   </si>
 </sst>
 </file>
@@ -860,13 +863,13 @@
         <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
